--- a/Datas/SkillZiWei.xlsx
+++ b/Datas/SkillZiWei.xlsx
@@ -1143,10 +1143,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="3">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="E5" s="3">
         <v>0.5</v>

--- a/Datas/SkillZiWei.xlsx
+++ b/Datas/SkillZiWei.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
   <si>
     <t>##var</t>
   </si>
@@ -37,6 +37,9 @@
     <t>ID</t>
   </si>
   <si>
+    <t>Duration</t>
+  </si>
+  <si>
     <t>GunCountPerSide</t>
   </si>
   <si>
@@ -71,6 +74,9 @@
   </si>
   <si>
     <t>参数ID</t>
+  </si>
+  <si>
+    <t>持续时间</t>
   </si>
   <si>
     <t>每侧猎枪数量</t>
@@ -1052,13 +1058,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="6" width="28.625" customWidth="1"/>
+    <col min="1" max="7" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:6">
+    <row r="1" ht="28" customHeight="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1077,82 +1083,97 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:6">
+    <row r="2" ht="28" customHeight="1" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:6">
+    <row r="3" ht="28" customHeight="1" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1" spans="1:6">
+    <row r="4" ht="28" customHeight="1" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="E4" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="F4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1" spans="1:6">
+    <row r="5" ht="28" customHeight="1" spans="1:7">
       <c r="B5" s="3">
         <v>1</v>
       </c>
       <c r="C5" s="3">
+        <v>10</v>
+      </c>
+      <c r="D5" s="3">
         <v>3</v>
       </c>
-      <c r="D5" s="3">
+      <c r="E5" s="3">
         <v>1</v>
       </c>
-      <c r="E5" s="3">
+      <c r="F5" s="3">
         <v>0.5</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>18</v>
+      <c r="G5" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/SkillZiWei.xlsx
+++ b/Datas/SkillZiWei.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
   <si>
     <t>##var</t>
   </si>
@@ -37,18 +37,15 @@
     <t>ID</t>
   </si>
   <si>
-    <t>Duration</t>
-  </si>
-  <si>
-    <t>GunCountPerSide</t>
-  </si>
-  <si>
-    <t>GunOffsetX</t>
+    <t>WeaponCountPerSide</t>
   </si>
   <si>
     <t>FireInterval</t>
   </si>
   <si>
+    <t>SkillPrefabResourcePath</t>
+  </si>
+  <si>
     <t>Comment</t>
   </si>
   <si>
@@ -76,19 +73,16 @@
     <t>参数ID</t>
   </si>
   <si>
-    <t>持续时间</t>
-  </si>
-  <si>
     <t>每侧猎枪数量</t>
   </si>
   <si>
-    <t>水平偏移</t>
-  </si>
-  <si>
     <t>射击间隔（秒）</t>
   </si>
   <si>
     <t>备注</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Prefabs/Skills/pf_skill_ziwei</t>
   </si>
   <si>
     <t>示例</t>
@@ -1058,13 +1052,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="6"/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="7" width="28.625" customWidth="1"/>
+    <col min="1" max="4" width="28.625" customWidth="1"/>
+    <col min="5" max="5" width="48.625" customWidth="1"/>
+    <col min="6" max="6" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:7">
+    <row r="1" ht="28" customHeight="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1083,22 +1079,19 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:6">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" ht="28" customHeight="1" spans="1:7">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>9</v>
@@ -1106,74 +1099,60 @@
       <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="1" t="s">
+    </row>
+    <row r="3" ht="28" customHeight="1" spans="1:6">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:7">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="4" ht="28" customHeight="1" spans="1:6">
+      <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>12</v>
+      <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1" spans="1:7">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:7">
+    <row r="5" ht="28" customHeight="1" spans="2:6">
       <c r="B5" s="3">
         <v>1</v>
       </c>
       <c r="C5" s="3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3">
-        <v>3</v>
-      </c>
-      <c r="E5" s="3">
-        <v>1</v>
-      </c>
-      <c r="F5" s="3">
         <v>0.5</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>20</v>
+      <c r="E5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/SkillZiWei.xlsx
+++ b/Datas/SkillZiWei.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>##var</t>
   </si>
@@ -43,9 +43,6 @@
     <t>FireInterval</t>
   </si>
   <si>
-    <t>SkillPrefabResourcePath</t>
-  </si>
-  <si>
     <t>Comment</t>
   </si>
   <si>
@@ -80,9 +77,6 @@
   </si>
   <si>
     <t>备注</t>
-  </si>
-  <si>
-    <t>Assets/Arts/Prefabs/Skills/pf_skill_ziwei</t>
   </si>
   <si>
     <t>示例</t>
@@ -1052,15 +1046,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="4" width="28.625" customWidth="1"/>
-    <col min="5" max="5" width="48.625" customWidth="1"/>
-    <col min="6" max="6" width="28.625" customWidth="1"/>
+    <col min="1" max="5" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:6">
+    <row r="1" ht="28" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1076,69 +1068,59 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:5">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:6">
-      <c r="A2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="1" t="s">
+    <row r="3" ht="28" customHeight="1" spans="1:5">
+      <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>9</v>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:6">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="4" ht="28" customHeight="1" spans="1:5">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>11</v>
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1" spans="1:6">
-      <c r="A4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="2:6">
+    <row r="5" ht="28" customHeight="1" spans="2:5">
       <c r="B5" s="3">
         <v>1</v>
       </c>
@@ -1149,10 +1131,7 @@
         <v>0.5</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/SkillZiWei.xlsx
+++ b/Datas/SkillZiWei.xlsx
@@ -79,7 +79,7 @@
     <t>备注</t>
   </si>
   <si>
-    <t>示例</t>
+    <t>/</t>
   </si>
 </sst>
 </file>

--- a/Datas/SkillZiWei.xlsx
+++ b/Datas/SkillZiWei.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>##var</t>
   </si>
@@ -43,9 +43,6 @@
     <t>FireInterval</t>
   </si>
   <si>
-    <t>Comment</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
@@ -55,9 +52,6 @@
     <t>float</t>
   </si>
   <si>
-    <t>string</t>
-  </si>
-  <si>
     <t>##group</t>
   </si>
   <si>
@@ -74,12 +68,6 @@
   </si>
   <si>
     <t>射击间隔（秒）</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>/</t>
   </si>
 </sst>
 </file>
@@ -1046,13 +1034,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="4"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="5" width="28.625" customWidth="1"/>
+    <col min="1" max="4" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:5">
+    <row r="1" ht="28" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1065,62 +1053,50 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:4">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:5">
-      <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
+    <row r="3" ht="28" customHeight="1" spans="1:4">
+      <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:5">
-      <c r="A3" s="1" t="s">
+    <row r="4" ht="28" customHeight="1" spans="1:4">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>10</v>
+      <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="2:5">
+    <row r="5" ht="28" customHeight="1" spans="2:4">
       <c r="B5" s="3">
         <v>1</v>
       </c>
@@ -1129,9 +1105,6 @@
       </c>
       <c r="D5" s="3">
         <v>0.5</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
